--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\table\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E390400-BBC1-4C28-9FED-CC8AF0CDF66D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -132,46 +126,47 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>list&lt;String&gt;{;}</t>
+  </si>
+  <si>
     <t>map&lt;int{_}int&gt;{;}</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>dropId</t>
+  </si>
+  <si>
+    <t>dropCondition</t>
+  </si>
+  <si>
     <t>triggerType</t>
   </si>
   <si>
+    <t>12001_0_100000</t>
+  </si>
+  <si>
     <t>10001_1000</t>
   </si>
   <si>
     <t>100006_100007_100008_100009_100010</t>
   </si>
   <si>
-    <t>dropId</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropCondition</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;String&gt;{;}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>12003_0_100000</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>12003_0_10000</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>12001_0_10000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,22 +189,159 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -223,29 +355,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,12 +365,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -267,51 +564,331 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 80" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -561,19 +1138,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="42.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="42.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.6416666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="42.6416666666667" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="28.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="12.875" style="2" customWidth="1"/>
@@ -588,7 +1165,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -602,85 +1179,88 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>13</v>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="4" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="2">
         <v>100011</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>14</v>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" s="2" customFormat="1" spans="1:4">
       <c r="A6" s="2">
         <v>2</v>
       </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" s="2" customFormat="1" spans="1:4">
       <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3">
       <c r="A8" s="2">
         <v>4</v>
       </c>
       <c r="B8" s="2">
         <v>100011</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>14</v>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -98,6 +98,29 @@
 每一行必出一个物品
 相同ID表示一个组
 一个组ID进行掉落时，需要把组内掉落包都走一遍</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+赌场掉落包
+</t>
         </r>
       </text>
     </comment>
@@ -1144,8 +1167,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
@@ -1257,6 +1280,78 @@
         <v>12</v>
       </c>
     </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2">
+        <v>10040</v>
+      </c>
+      <c r="B9"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>10050</v>
+      </c>
+      <c r="B10"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>10060</v>
+      </c>
+      <c r="B11"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
+        <v>10070</v>
+      </c>
+      <c r="B12"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2">
+        <v>10080</v>
+      </c>
+      <c r="B13"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>10090</v>
+      </c>
+      <c r="B14"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2">
+        <v>10100</v>
+      </c>
+      <c r="B15"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2">
+        <v>10110</v>
+      </c>
+      <c r="B16"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2">
+        <v>10120</v>
+      </c>
+      <c r="B17"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2">
+        <v>10130</v>
+      </c>
+      <c r="B18"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2">
+        <v>10140</v>
+      </c>
+      <c r="B19"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2">
+        <v>10150</v>
+      </c>
+      <c r="B20"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>序号ID</t>
   </si>
@@ -177,6 +177,36 @@
   </si>
   <si>
     <t>12001_0_10000</t>
+  </si>
+  <si>
+    <t>12002_500</t>
+  </si>
+  <si>
+    <t>12002_1000</t>
+  </si>
+  <si>
+    <t>12002_2000</t>
+  </si>
+  <si>
+    <t>12002_3000</t>
+  </si>
+  <si>
+    <t>12002_5000</t>
+  </si>
+  <si>
+    <t>12002_7500</t>
+  </si>
+  <si>
+    <t>12002_10000</t>
+  </si>
+  <si>
+    <t>12002_12500</t>
+  </si>
+  <si>
+    <t>12002_15000</t>
+  </si>
+  <si>
+    <t>12002_40000</t>
   </si>
 </sst>
 </file>
@@ -836,7 +866,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -853,6 +883,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1280,77 +1313,137 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
-      <c r="B9"/>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="B9" s="6">
+        <v>10010040</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
-      <c r="B10"/>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="B10" s="6">
+        <v>10010050</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
-      <c r="B11"/>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="B11" s="6">
+        <v>10010060</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
-      <c r="B12"/>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="B12" s="6">
+        <v>10010070</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
-      <c r="B13"/>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="B13" s="6">
+        <v>10010080</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
-      <c r="B14"/>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="B14" s="6">
+        <v>10010090</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
-      <c r="B15"/>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="B15" s="6">
+        <v>10010100</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
-      <c r="B16"/>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="B16" s="6">
+        <v>10010110</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2">
         <v>10120</v>
       </c>
-      <c r="B17"/>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="B17" s="6">
+        <v>10010120</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="2">
         <v>10130</v>
       </c>
-      <c r="B18"/>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="B18" s="6">
+        <v>10010130</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="2">
         <v>10140</v>
       </c>
-      <c r="B19"/>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="B19" s="6">
+        <v>10010140</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="2">
         <v>10150</v>
       </c>
-      <c r="B20"/>
+      <c r="B20" s="6">
+        <v>10010150</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\table\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE2578B-AEE4-42FF-A886-61B71877B872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -77,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -101,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A9" authorId="0">
+    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -212,14 +218,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,159 +242,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -408,8 +271,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,198 +287,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -617,254 +300,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -889,62 +330,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 80" xfId="49"/>
+    <cellStyle name="常规 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1194,19 +591,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="42.6416666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="42.6416666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="42.625" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="28.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="12.875" style="2" customWidth="1"/>
@@ -1221,7 +618,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1235,7 +632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1249,7 +646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="3" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1263,13 +660,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="4" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1280,17 +677,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1300,9 +695,8 @@
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:3">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1313,142 +707,142 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
       <c r="B9" s="6">
-        <v>10010040</v>
+        <v>10040</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
       <c r="B10" s="6">
-        <v>10010050</v>
+        <v>10050</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
       <c r="B11" s="6">
-        <v>10010060</v>
+        <v>10060</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
       <c r="B12" s="6">
-        <v>10010070</v>
+        <v>10070</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
       <c r="B13" s="6">
-        <v>10010080</v>
+        <v>10080</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
       <c r="B14" s="6">
-        <v>10010090</v>
+        <v>10090</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
       <c r="B15" s="6">
-        <v>10010100</v>
+        <v>10100</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
       <c r="B16" s="6">
-        <v>10010110</v>
+        <v>10110</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
         <v>10120</v>
       </c>
       <c r="B17" s="6">
-        <v>10010120</v>
+        <v>10120</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
         <v>10130</v>
       </c>
       <c r="B18" s="6">
-        <v>10010130</v>
+        <v>10130</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
         <v>10140</v>
       </c>
       <c r="B19" s="6">
-        <v>10010140</v>
+        <v>10140</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
         <v>10150</v>
       </c>
       <c r="B20" s="6">
-        <v>10010150</v>
+        <v>10150</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\project\table\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE2578B-AEE4-42FF-A886-61B71877B872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="A9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -218,8 +212,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,22 +242,159 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,14 +408,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,12 +418,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -300,12 +617,254 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -330,18 +889,62 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 80" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 80" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -591,19 +1194,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="42.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="42.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.6416666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="42.6416666666667" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="28.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="12.875" style="2" customWidth="1"/>
@@ -618,7 +1221,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -632,7 +1235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -646,7 +1249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -660,13 +1263,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -677,15 +1280,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="6" s="2" customFormat="1" spans="1:4">
       <c r="A6" s="2">
         <v>2</v>
       </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="7" s="2" customFormat="1" spans="1:4">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -695,8 +1300,9 @@
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -707,7 +1313,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
@@ -718,7 +1324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
@@ -729,7 +1335,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
@@ -740,7 +1346,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
@@ -751,7 +1357,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
@@ -762,7 +1368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
@@ -773,7 +1379,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
@@ -784,7 +1390,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
@@ -795,7 +1401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3">
       <c r="A17" s="2">
         <v>10120</v>
       </c>
@@ -806,7 +1412,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3">
       <c r="A18" s="2">
         <v>10130</v>
       </c>
@@ -817,7 +1423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3">
       <c r="A19" s="2">
         <v>10140</v>
       </c>
@@ -828,7 +1434,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3">
       <c r="A20" s="2">
         <v>10150</v>
       </c>
@@ -840,9 +1446,9 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -1318,7 +1318,7 @@
         <v>10040</v>
       </c>
       <c r="B9" s="6">
-        <v>10010040</v>
+        <v>10040</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
@@ -1329,7 +1329,7 @@
         <v>10050</v>
       </c>
       <c r="B10" s="6">
-        <v>10010050</v>
+        <v>10050</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>16</v>
@@ -1340,7 +1340,7 @@
         <v>10060</v>
       </c>
       <c r="B11" s="6">
-        <v>10010060</v>
+        <v>10060</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -1351,7 +1351,7 @@
         <v>10070</v>
       </c>
       <c r="B12" s="6">
-        <v>10010070</v>
+        <v>10070</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
@@ -1362,7 +1362,7 @@
         <v>10080</v>
       </c>
       <c r="B13" s="6">
-        <v>10010080</v>
+        <v>10080</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>18</v>
@@ -1373,7 +1373,7 @@
         <v>10090</v>
       </c>
       <c r="B14" s="6">
-        <v>10010090</v>
+        <v>10090</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>19</v>
@@ -1384,7 +1384,7 @@
         <v>10100</v>
       </c>
       <c r="B15" s="6">
-        <v>10010100</v>
+        <v>10100</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>20</v>
@@ -1395,7 +1395,7 @@
         <v>10110</v>
       </c>
       <c r="B16" s="6">
-        <v>10010110</v>
+        <v>10110</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
@@ -1406,7 +1406,7 @@
         <v>10120</v>
       </c>
       <c r="B17" s="6">
-        <v>10010120</v>
+        <v>10120</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>22</v>
@@ -1417,7 +1417,7 @@
         <v>10130</v>
       </c>
       <c r="B18" s="6">
-        <v>10010130</v>
+        <v>10130</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>23</v>
@@ -1428,7 +1428,7 @@
         <v>10140</v>
       </c>
       <c r="B19" s="6">
-        <v>10010140</v>
+        <v>10140</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>24</v>
@@ -1439,7 +1439,7 @@
         <v>10150</v>
       </c>
       <c r="B20" s="6">
-        <v>10010150</v>
+        <v>10150</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>

--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>序号ID</t>
   </si>
@@ -179,34 +179,40 @@
     <t>12001_0_10000</t>
   </si>
   <si>
-    <t>12002_500</t>
-  </si>
-  <si>
-    <t>12002_1000</t>
-  </si>
-  <si>
-    <t>12002_2000</t>
-  </si>
-  <si>
-    <t>12002_3000</t>
-  </si>
-  <si>
-    <t>12002_5000</t>
-  </si>
-  <si>
-    <t>12002_7500</t>
-  </si>
-  <si>
-    <t>12002_10000</t>
-  </si>
-  <si>
-    <t>12002_12500</t>
-  </si>
-  <si>
-    <t>12002_15000</t>
+    <t>12002_20000</t>
   </si>
   <si>
     <t>12002_40000</t>
+  </si>
+  <si>
+    <t>12002_60000</t>
+  </si>
+  <si>
+    <t>12002_85000</t>
+  </si>
+  <si>
+    <t>12002_150000</t>
+  </si>
+  <si>
+    <t>12002_300000</t>
+  </si>
+  <si>
+    <t>12002_450000</t>
+  </si>
+  <si>
+    <t>12002_700000</t>
+  </si>
+  <si>
+    <t>12002_920000</t>
+  </si>
+  <si>
+    <t>12002_1250000</t>
+  </si>
+  <si>
+    <t>12002_1800000</t>
+  </si>
+  <si>
+    <t>12002_2500000</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1338,7 @@
         <v>10050</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1343,7 +1349,7 @@
         <v>10060</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1354,7 +1360,7 @@
         <v>10070</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1365,7 +1371,7 @@
         <v>10080</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1376,7 +1382,7 @@
         <v>10090</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1387,7 +1393,7 @@
         <v>10100</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1398,7 +1404,7 @@
         <v>10110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1409,7 +1415,7 @@
         <v>10120</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1420,7 +1426,7 @@
         <v>10130</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1431,7 +1437,7 @@
         <v>10140</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1442,7 +1448,7 @@
         <v>10150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="dropConfig" sheetId="1" r:id="rId1"/>
@@ -149,7 +149,7 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>list&lt;String&gt;{;}</t>
+    <t>string</t>
   </si>
   <si>
     <t>map&lt;int{_}int&gt;{;}</t>
@@ -167,7 +167,7 @@
     <t>triggerType</t>
   </si>
   <si>
-    <t>12001_0_100000</t>
+    <t>effectiveBetAll(0,100000)</t>
   </si>
   <si>
     <t>10001_1000</t>
@@ -176,43 +176,43 @@
     <t>100006_100007_100008_100009_100010</t>
   </si>
   <si>
-    <t>12001_0_10000</t>
-  </si>
-  <si>
-    <t>12002_20000</t>
-  </si>
-  <si>
-    <t>12002_40000</t>
-  </si>
-  <si>
-    <t>12002_60000</t>
-  </si>
-  <si>
-    <t>12002_85000</t>
-  </si>
-  <si>
-    <t>12002_150000</t>
-  </si>
-  <si>
-    <t>12002_300000</t>
-  </si>
-  <si>
-    <t>12002_450000</t>
-  </si>
-  <si>
-    <t>12002_700000</t>
-  </si>
-  <si>
-    <t>12002_920000</t>
-  </si>
-  <si>
-    <t>12002_1250000</t>
-  </si>
-  <si>
-    <t>12002_1800000</t>
-  </si>
-  <si>
-    <t>12002_2500000</t>
+    <t>effectiveBetAll(0,10000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(20000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(40000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(60000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(85000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(150000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(300000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(450000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(700000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(920000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1250000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1800000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(2500000)</t>
   </si>
 </sst>
 </file>
@@ -872,7 +872,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -890,6 +890,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1248,7 +1251,7 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1275,11 +1278,11 @@
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <v>100011</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1290,7 +1293,7 @@
       <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -1300,7 +1303,7 @@
       <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1308,99 +1311,99 @@
       </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <v>100011</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>10040</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>10050</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>10060</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>10070</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>10080</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>10090</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>10100</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>10110</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1411,7 +1414,7 @@
       <c r="A17" s="2">
         <v>10120</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>10120</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1422,7 +1425,7 @@
       <c r="A18" s="2">
         <v>10130</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>10130</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1433,7 +1436,7 @@
       <c r="A19" s="2">
         <v>10140</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>10140</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1444,7 +1447,7 @@
       <c r="A20" s="2">
         <v>10150</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>10150</v>
       </c>
       <c r="C20" s="2" t="s">

--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -179,40 +179,40 @@
     <t>effectiveBetAll(0,10000)</t>
   </si>
   <si>
-    <t>effectiveBet(20000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(40000)</t>
-  </si>
-  <si>
     <t>effectiveBet(60000)</t>
   </si>
   <si>
-    <t>effectiveBet(85000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(150000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(300000)</t>
+    <t>effectiveBet(120000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(180000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(255000)</t>
   </si>
   <si>
     <t>effectiveBet(450000)</t>
   </si>
   <si>
-    <t>effectiveBet(700000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(920000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(1250000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(1800000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(2500000)</t>
+    <t>effectiveBet(900000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1350000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(2100000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(2760000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(3750000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(5400000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(7500000)</t>
   </si>
 </sst>
 </file>
@@ -872,7 +872,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -895,6 +895,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1209,8 +1212,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
@@ -1230,7 +1233,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1244,7 +1247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1272,13 +1275,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:5">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1288,8 +1291,10 @@
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:4">
+      <c r="D5" s="8"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:5">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1298,8 +1303,9 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:4">
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:5">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1309,9 +1315,10 @@
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7" s="8"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1321,8 +1328,10 @@
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8" s="8"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
@@ -1333,7 +1342,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
@@ -1343,8 +1352,9 @@
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
@@ -1354,8 +1364,9 @@
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
@@ -1365,8 +1376,9 @@
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
@@ -1376,8 +1388,9 @@
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
@@ -1387,8 +1400,9 @@
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
@@ -1398,8 +1412,9 @@
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
@@ -1409,8 +1424,9 @@
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="2">
         <v>10120</v>
       </c>
@@ -1420,8 +1436,9 @@
       <c r="C17" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="2">
         <v>10130</v>
       </c>
@@ -1431,8 +1448,9 @@
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="8"/>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="2">
         <v>10140</v>
       </c>
@@ -1442,8 +1460,9 @@
       <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="2">
         <v>10150</v>
       </c>
@@ -1453,6 +1472,7 @@
       <c r="C20" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="D20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/dropConfig.xlsx
+++ b/table/resources/sample/dropConfig.xlsx
@@ -179,40 +179,40 @@
     <t>effectiveBetAll(0,10000)</t>
   </si>
   <si>
+    <t>effectiveBet(20000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(40000)</t>
+  </si>
+  <si>
     <t>effectiveBet(60000)</t>
   </si>
   <si>
-    <t>effectiveBet(120000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(180000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(255000)</t>
+    <t>effectiveBet(85000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(150000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(300000)</t>
   </si>
   <si>
     <t>effectiveBet(450000)</t>
   </si>
   <si>
-    <t>effectiveBet(900000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(1350000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(2100000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(2760000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(3750000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(5400000)</t>
-  </si>
-  <si>
-    <t>effectiveBet(7500000)</t>
+    <t>effectiveBet(700000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(920000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1250000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(1800000)</t>
+  </si>
+  <si>
+    <t>effectiveBet(2500000)</t>
   </si>
 </sst>
 </file>
@@ -872,7 +872,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -895,9 +895,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1212,8 +1209,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
     <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
@@ -1233,7 +1230,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1247,7 +1244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1261,7 +1258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1275,13 +1272,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:5">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:4">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1291,10 +1288,8 @@
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:5">
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:4">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1303,9 +1298,8 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:5">
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:4">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1315,10 +1309,9 @@
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1328,10 +1321,8 @@
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2">
         <v>10040</v>
       </c>
@@ -1342,7 +1333,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:4">
       <c r="A10" s="2">
         <v>10050</v>
       </c>
@@ -1352,9 +1343,8 @@
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:5">
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2">
         <v>10060</v>
       </c>
@@ -1364,9 +1354,8 @@
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:5">
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2">
         <v>10070</v>
       </c>
@@ -1376,9 +1365,8 @@
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="1:5">
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2">
         <v>10080</v>
       </c>
@@ -1388,9 +1376,8 @@
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:5">
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2">
         <v>10090</v>
       </c>
@@ -1400,9 +1387,8 @@
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:5">
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2">
         <v>10100</v>
       </c>
@@ -1412,9 +1398,8 @@
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:5">
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2">
         <v>10110</v>
       </c>
@@ -1424,9 +1409,8 @@
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="8"/>
-    </row>
-    <row r="17" spans="1:4">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2">
         <v>10120</v>
       </c>
@@ -1436,9 +1420,8 @@
       <c r="C17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="8"/>
-    </row>
-    <row r="18" spans="1:4">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="2">
         <v>10130</v>
       </c>
@@ -1448,9 +1431,8 @@
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="8"/>
-    </row>
-    <row r="19" spans="1:4">
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="2">
         <v>10140</v>
       </c>
@@ -1460,9 +1442,8 @@
       <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="8"/>
-    </row>
-    <row r="20" spans="1:4">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="2">
         <v>10150</v>
       </c>
@@ -1472,7 +1453,6 @@
       <c r="C20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
